--- a/LoanOfficer-A/2023/32 minakumari.xlsx
+++ b/LoanOfficer-A/2023/32 minakumari.xlsx
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>1050</v>
+        <v>1400</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>15750</v>
+        <v>15400</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -959,9 +959,15 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="1"/>
+      <c r="B6" s="3">
+        <v>45420</v>
+      </c>
+      <c r="C6" s="4">
+        <v>350</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
       <c r="E6" s="1">
         <v>34</v>
       </c>

--- a/LoanOfficer-A/2023/32 minakumari.xlsx
+++ b/LoanOfficer-A/2023/32 minakumari.xlsx
@@ -606,7 +606,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>1400</v>
+        <v>1750</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>15400</v>
+        <v>15050</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -991,9 +991,15 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="1"/>
+      <c r="B7" s="3">
+        <v>45427</v>
+      </c>
+      <c r="C7" s="4">
+        <v>350</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
       <c r="E7" s="1">
         <v>35</v>
       </c>

--- a/LoanOfficer-A/2023/32 minakumari.xlsx
+++ b/LoanOfficer-A/2023/32 minakumari.xlsx
@@ -606,7 +606,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>1750</v>
+        <v>2450</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>15050</v>
+        <v>14350</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1023,9 +1023,15 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="1"/>
+      <c r="B8" s="3">
+        <v>45437</v>
+      </c>
+      <c r="C8" s="4">
+        <v>350</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
       <c r="E8" s="1">
         <v>36</v>
       </c>
@@ -1049,9 +1055,15 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="1"/>
+      <c r="B9" s="3">
+        <v>45444</v>
+      </c>
+      <c r="C9" s="4">
+        <v>350</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
       <c r="E9" s="1">
         <v>37</v>
       </c>

--- a/LoanOfficer-A/2023/32 minakumari.xlsx
+++ b/LoanOfficer-A/2023/32 minakumari.xlsx
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>2450</v>
+        <v>4550</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>14350</v>
+        <v>12250</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1087,9 +1087,15 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="1"/>
+      <c r="B10" s="3">
+        <v>45449</v>
+      </c>
+      <c r="C10" s="4">
+        <v>350</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
       <c r="E10" s="1">
         <v>38</v>
       </c>
@@ -1113,9 +1119,15 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="1"/>
+      <c r="B11" s="3">
+        <v>45455</v>
+      </c>
+      <c r="C11" s="4">
+        <v>350</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
       <c r="E11" s="1">
         <v>39</v>
       </c>
@@ -1139,9 +1151,15 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="1"/>
+      <c r="B12" s="3">
+        <v>45465</v>
+      </c>
+      <c r="C12" s="4">
+        <v>350</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
       <c r="E12" s="1">
         <v>40</v>
       </c>
@@ -1165,9 +1183,15 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="1"/>
+      <c r="B13" s="3">
+        <v>45470</v>
+      </c>
+      <c r="C13" s="4">
+        <v>350</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
       <c r="E13" s="1">
         <v>41</v>
       </c>
@@ -1191,9 +1215,15 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="1"/>
+      <c r="B14" s="3">
+        <v>45474</v>
+      </c>
+      <c r="C14" s="4">
+        <v>350</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
       <c r="E14" s="1">
         <v>42</v>
       </c>
@@ -1217,9 +1247,15 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="1"/>
+      <c r="B15" s="3">
+        <v>45484</v>
+      </c>
+      <c r="C15" s="4">
+        <v>350</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
       <c r="E15" s="1">
         <v>43</v>
       </c>

--- a/LoanOfficer-A/2023/32 minakumari.xlsx
+++ b/LoanOfficer-A/2023/32 minakumari.xlsx
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>4550</v>
+        <v>5250</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>12250</v>
+        <v>11550</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1279,9 +1279,15 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="1"/>
+      <c r="B16" s="3">
+        <v>45490</v>
+      </c>
+      <c r="C16" s="4">
+        <v>350</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
       <c r="E16" s="1">
         <v>44</v>
       </c>
@@ -1305,9 +1311,15 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="1"/>
+      <c r="B17" s="3">
+        <v>45495</v>
+      </c>
+      <c r="C17" s="4">
+        <v>350</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
       <c r="E17" s="1">
         <v>45</v>
       </c>

--- a/LoanOfficer-A/2023/32 minakumari.xlsx
+++ b/LoanOfficer-A/2023/32 minakumari.xlsx
@@ -606,7 +606,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>5250</v>
+        <v>8400</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>11550</v>
+        <v>8400</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1343,9 +1343,15 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="1"/>
+      <c r="B18" s="3">
+        <v>45506</v>
+      </c>
+      <c r="C18" s="4">
+        <v>350</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
       <c r="E18" s="1">
         <v>46</v>
       </c>
@@ -1369,9 +1375,15 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="1"/>
+      <c r="B19" s="3">
+        <v>45512</v>
+      </c>
+      <c r="C19" s="4">
+        <v>350</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
       <c r="E19" s="1">
         <v>47</v>
       </c>
@@ -1395,9 +1407,15 @@
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="1"/>
+      <c r="B20" s="3">
+        <v>45522</v>
+      </c>
+      <c r="C20" s="4">
+        <v>350</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
       <c r="E20" s="1">
         <v>48</v>
       </c>
@@ -1421,9 +1439,15 @@
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="1"/>
+      <c r="B21" s="3">
+        <v>45525</v>
+      </c>
+      <c r="C21" s="4">
+        <v>350</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
       <c r="E21" s="1">
         <v>49</v>
       </c>
@@ -1447,9 +1471,15 @@
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="1"/>
+      <c r="B22" s="3">
+        <v>45534</v>
+      </c>
+      <c r="C22" s="4">
+        <v>350</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
@@ -1473,9 +1503,15 @@
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="1"/>
+      <c r="B23" s="3">
+        <v>45540</v>
+      </c>
+      <c r="C23" s="4">
+        <v>350</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
       <c r="E23" s="1">
         <v>51</v>
       </c>
@@ -1499,9 +1535,15 @@
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="1"/>
+      <c r="B24" s="3">
+        <v>45550</v>
+      </c>
+      <c r="C24" s="4">
+        <v>350</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
       <c r="E24" s="1">
         <v>52</v>
       </c>
@@ -1525,9 +1567,15 @@
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="1"/>
+      <c r="B25" s="3">
+        <v>45558</v>
+      </c>
+      <c r="C25" s="4">
+        <v>350</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
       <c r="E25" s="1">
         <v>53</v>
       </c>
@@ -1551,9 +1599,15 @@
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="1"/>
+      <c r="B26" s="3">
+        <v>45561</v>
+      </c>
+      <c r="C26" s="4">
+        <v>350</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
       <c r="E26" s="1">
         <v>54</v>
       </c>

--- a/LoanOfficer-A/2023/32 minakumari.xlsx
+++ b/LoanOfficer-A/2023/32 minakumari.xlsx
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>8400</v>
+        <v>9100</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>8400</v>
+        <v>7700</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1631,9 +1631,15 @@
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="1"/>
+      <c r="B27" s="3">
+        <v>45572</v>
+      </c>
+      <c r="C27" s="4">
+        <v>350</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
       <c r="E27" s="1">
         <v>55</v>
       </c>
@@ -1657,9 +1663,15 @@
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="1"/>
+      <c r="B28" s="3">
+        <v>45575</v>
+      </c>
+      <c r="C28" s="4">
+        <v>350</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
       <c r="E28" s="1">
         <v>56</v>
       </c>

--- a/LoanOfficer-A/2023/32 minakumari.xlsx
+++ b/LoanOfficer-A/2023/32 minakumari.xlsx
@@ -606,7 +606,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>9100</v>
+        <v>9450</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>7700</v>
+        <v>7350</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1695,9 +1695,15 @@
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="1"/>
+      <c r="B29" s="3">
+        <v>45582</v>
+      </c>
+      <c r="C29" s="4">
+        <v>350</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
       <c r="E29" s="1">
         <v>57</v>
       </c>

--- a/LoanOfficer-A/2023/32 minakumari.xlsx
+++ b/LoanOfficer-A/2023/32 minakumari.xlsx
@@ -606,7 +606,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>9450</v>
+        <v>10500</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>7350</v>
+        <v>6300</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1727,9 +1727,15 @@
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="1"/>
+      <c r="B30" s="3">
+        <v>45587</v>
+      </c>
+      <c r="C30" s="4">
+        <v>350</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
       <c r="E30" s="1">
         <v>58</v>
       </c>
@@ -1753,9 +1759,15 @@
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="1"/>
+      <c r="B31" s="3">
+        <v>45595</v>
+      </c>
+      <c r="C31" s="4">
+        <v>350</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
       <c r="E31" s="1">
         <v>59</v>
       </c>
@@ -1779,9 +1791,15 @@
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="1"/>
+      <c r="B32" s="3">
+        <v>45602</v>
+      </c>
+      <c r="C32" s="4">
+        <v>350</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
       <c r="E32" s="1">
         <v>60</v>
       </c>

--- a/LoanOfficer-A/2023/32 minakumari.xlsx
+++ b/LoanOfficer-A/2023/32 minakumari.xlsx
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>10500</v>
+        <v>11200</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>6300</v>
+        <v>5600</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -875,9 +875,15 @@
       <c r="E3" s="1">
         <v>31</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="1"/>
+      <c r="F3" s="3">
+        <v>45610</v>
+      </c>
+      <c r="G3" s="4">
+        <v>350</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
       <c r="I3" s="1">
         <v>61</v>
       </c>
@@ -907,9 +913,15 @@
       <c r="E4" s="1">
         <v>32</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="1"/>
+      <c r="F4" s="3">
+        <v>45618</v>
+      </c>
+      <c r="G4" s="4">
+        <v>350</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
       <c r="I4" s="1">
         <v>62</v>
       </c>

--- a/LoanOfficer-A/2023/32 minakumari.xlsx
+++ b/LoanOfficer-A/2023/32 minakumari.xlsx
@@ -606,7 +606,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>11200</v>
+        <v>11550</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>5600</v>
+        <v>5250</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -951,9 +951,15 @@
       <c r="E5" s="1">
         <v>33</v>
       </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="1"/>
+      <c r="F5" s="3">
+        <v>45625</v>
+      </c>
+      <c r="G5" s="4">
+        <v>350</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
       <c r="I5" s="1">
         <v>63</v>
       </c>

--- a/LoanOfficer-A/2023/32 minakumari.xlsx
+++ b/LoanOfficer-A/2023/32 minakumari.xlsx
@@ -606,7 +606,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>11550</v>
+        <v>11900</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>5250</v>
+        <v>4900</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -989,9 +989,15 @@
       <c r="E6" s="1">
         <v>34</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="1"/>
+      <c r="F6" s="3">
+        <v>45632</v>
+      </c>
+      <c r="G6" s="4">
+        <v>350</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
       <c r="I6" s="1">
         <v>64</v>
       </c>

--- a/LoanOfficer-A/2023/32 minakumari.xlsx
+++ b/LoanOfficer-A/2023/32 minakumari.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t xml:space="preserve">Loan Amount: </t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>Paid (weeks):</t>
+  </si>
+  <si>
+    <t>date of completion</t>
   </si>
 </sst>
 </file>
@@ -217,7 +220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -278,6 +281,9 @@
     </xf>
     <xf numFmtId="15" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -624,8 +630,8 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="13"/>
@@ -705,20 +711,20 @@
       <c r="C16" s="14"/>
     </row>
     <row r="17" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="22"/>
+      <c r="C17" s="23"/>
     </row>
     <row r="19" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
     </row>
     <row r="21" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="22"/>
+      <c r="C21" s="23"/>
     </row>
     <row r="22" spans="2:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B22" s="14"/>
@@ -813,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>11900</v>
+        <v>12600</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -837,8 +843,13 @@
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="7"/>
+      <c r="F2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="21">
+        <f>B3+(48-1)*7</f>
+        <v>45728</v>
+      </c>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
       <c r="J2" s="7" t="s">
@@ -846,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>4900</v>
+        <v>4200</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1027,9 +1038,15 @@
       <c r="E7" s="1">
         <v>35</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="1"/>
+      <c r="F7" s="3">
+        <v>45640</v>
+      </c>
+      <c r="G7" s="4">
+        <v>350</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
       <c r="I7" s="1">
         <v>65</v>
       </c>
@@ -1059,9 +1076,15 @@
       <c r="E8" s="1">
         <v>36</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="1"/>
+      <c r="F8" s="3">
+        <v>45645</v>
+      </c>
+      <c r="G8" s="4">
+        <v>350</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
       <c r="I8" s="1">
         <v>66</v>
       </c>

--- a/LoanOfficer-A/2023/32 minakumari.xlsx
+++ b/LoanOfficer-A/2023/32 minakumari.xlsx
@@ -612,7 +612,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>12600</v>
+        <v>12950</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>4200</v>
+        <v>3850</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1114,9 +1114,15 @@
       <c r="E9" s="1">
         <v>37</v>
       </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="1"/>
+      <c r="F9" s="3">
+        <v>45651</v>
+      </c>
+      <c r="G9" s="4">
+        <v>350</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
       <c r="I9" s="1">
         <v>67</v>
       </c>

--- a/LoanOfficer-A/2023/32 minakumari.xlsx
+++ b/LoanOfficer-A/2023/32 minakumari.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>12950</v>
+        <v>14000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>3850</v>
+        <v>2800</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1152,9 +1152,15 @@
       <c r="E10" s="1">
         <v>38</v>
       </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="1"/>
+      <c r="F10" s="3">
+        <v>45670</v>
+      </c>
+      <c r="G10" s="4">
+        <v>350</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
       <c r="I10" s="1">
         <v>68</v>
       </c>
@@ -1184,9 +1190,15 @@
       <c r="E11" s="1">
         <v>39</v>
       </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="1"/>
+      <c r="F11" s="3">
+        <v>45670</v>
+      </c>
+      <c r="G11" s="4">
+        <v>350</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
       <c r="I11" s="1">
         <v>69</v>
       </c>
@@ -1216,9 +1228,15 @@
       <c r="E12" s="1">
         <v>40</v>
       </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="1"/>
+      <c r="F12" s="3">
+        <v>45673</v>
+      </c>
+      <c r="G12" s="4">
+        <v>350</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
       <c r="I12" s="1">
         <v>70</v>
       </c>

--- a/LoanOfficer-A/2023/32 minakumari.xlsx
+++ b/LoanOfficer-A/2023/32 minakumari.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>14000</v>
+        <v>14700</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>2800</v>
+        <v>2100</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1266,9 +1266,15 @@
       <c r="E13" s="1">
         <v>41</v>
       </c>
-      <c r="F13" s="1"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="1"/>
+      <c r="F13" s="3">
+        <v>45689</v>
+      </c>
+      <c r="G13" s="4">
+        <v>350</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
       <c r="I13" s="1">
         <v>71</v>
       </c>
@@ -1298,9 +1304,15 @@
       <c r="E14" s="1">
         <v>42</v>
       </c>
-      <c r="F14" s="1"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="1"/>
+      <c r="F14" s="3">
+        <v>45689</v>
+      </c>
+      <c r="G14" s="4">
+        <v>350</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
       <c r="I14" s="1">
         <v>72</v>
       </c>

--- a/LoanOfficer-A/2023/32 minakumari.xlsx
+++ b/LoanOfficer-A/2023/32 minakumari.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>14700</v>
+        <v>15400</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>2100</v>
+        <v>1400</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1342,9 +1342,15 @@
       <c r="E15" s="1">
         <v>43</v>
       </c>
-      <c r="F15" s="1"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="1"/>
+      <c r="F15" s="3">
+        <v>45698</v>
+      </c>
+      <c r="G15" s="4">
+        <v>350</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1</v>
+      </c>
       <c r="I15" s="1">
         <v>73</v>
       </c>
@@ -1374,9 +1380,15 @@
       <c r="E16" s="1">
         <v>44</v>
       </c>
-      <c r="F16" s="1"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="1"/>
+      <c r="F16" s="3">
+        <v>45702</v>
+      </c>
+      <c r="G16" s="4">
+        <v>350</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
       <c r="I16" s="1">
         <v>74</v>
       </c>

--- a/LoanOfficer-A/2023/32 minakumari.xlsx
+++ b/LoanOfficer-A/2023/32 minakumari.xlsx
@@ -612,7 +612,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>15400</v>
+        <v>16450</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>1400</v>
+        <v>350</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1418,9 +1418,15 @@
       <c r="E17" s="1">
         <v>45</v>
       </c>
-      <c r="F17" s="1"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="1"/>
+      <c r="F17" s="3">
+        <v>45706</v>
+      </c>
+      <c r="G17" s="4">
+        <v>350</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1</v>
+      </c>
       <c r="I17" s="1">
         <v>75</v>
       </c>
@@ -1450,9 +1456,15 @@
       <c r="E18" s="1">
         <v>46</v>
       </c>
-      <c r="F18" s="1"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="1"/>
+      <c r="F18" s="3">
+        <v>45710</v>
+      </c>
+      <c r="G18" s="4">
+        <v>350</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
       <c r="I18" s="1">
         <v>76</v>
       </c>
@@ -1482,9 +1494,15 @@
       <c r="E19" s="1">
         <v>47</v>
       </c>
-      <c r="F19" s="1"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="1"/>
+      <c r="F19" s="3">
+        <v>45710</v>
+      </c>
+      <c r="G19" s="4">
+        <v>350</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1</v>
+      </c>
       <c r="I19" s="1">
         <v>77</v>
       </c>
